--- a/data/trans_dic/IP31KM11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,84; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,62; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,43; 100,0</t>
+          <t>95,58; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,93; 99,59</t>
+          <t>95,73; 98,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,99; 98,31</t>
+          <t>97,58; 99,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,27; 98,75</t>
+          <t>97,16; 98,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,04; 100,0</t>
+          <t>94,41; 98,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94,19; 98,77</t>
+          <t>97,4; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,61; 99,08</t>
+          <t>96,47; 99,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98,11; 99,46</t>
+          <t>96,41; 98,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,87; 98,27</t>
+          <t>97,94; 99,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,65</t>
+          <t>97,45; 98,75</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>98295</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48778; 53699</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41138; 45905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108043; 112043</t>
+          <t>95218; 99620</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>618</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>447379</t>
+          <t>454527</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>488410</t>
+          <t>419875</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>935789</t>
+          <t>874403</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>442480; 449968</t>
+          <t>446517; 459981</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>464793; 496708</t>
+          <t>414399; 422652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>911839; 945161</t>
+          <t>865784; 880546</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>145057</t>
+          <t>161844</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>176091</t>
+          <t>146124</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321147</t>
+          <t>307967</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>141853; 146186</t>
+          <t>157368; 164480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170617; 178913</t>
+          <t>143308; 147140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316242; 324310</t>
+          <t>302734; 310850</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>903</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>644845</t>
+          <t>670086</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>610580</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1367690</t>
+          <t>1280666</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>639401; 648204</t>
+          <t>662166; 676812</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699061; 731853</t>
+          <t>605009; 614005</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1347234; 1377659</t>
+          <t>1271217; 1288279</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>89,62; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95,58; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>95,73; 98,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>97,58; 99,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97,16; 98,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>94,41; 98,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>97,4; 100,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>96,47; 99,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>96,41; 98,54</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97,94; 99,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97,45; 98,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9711454810002285</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9867038047871917</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44580</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98295</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.8961643059017026</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9558096836841832</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>41138; 45905</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>95218; 99620</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9744948758344594</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9887181835426928</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9812732737978681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>454527</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>419875</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>874403</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9573218587515014</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9758231180557516</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9716015301176355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>446517; 459981</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>414399; 422652</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>865784; 880546</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9861886414924003</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9952576589013253</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9881672349565666</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9709523140692958</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9930969156277903</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9813350026196778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>161844</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>146124</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>307967</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9440966239755533</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9739548035306408</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9646580325223086</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>157368; 164480</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>143308; 147140</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>302734; 310850</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9867674040713412</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9905189729204258</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9756298204601374</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9884553004694351</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9817028208056462</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>670086</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>610580</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1280666</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9640991007794146</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9794365501153535</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9744595069813372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>662166; 676812</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>605009; 614005</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1271217; 1288279</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9854231660315677</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9940010133520577</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9875389006544705</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>53715</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>44580</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>98295</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>41138</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>95218</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>99620</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>616</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>618</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>454527</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>419875</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>874403</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>446517</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>414399</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>865784</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>459981</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>422652</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>880546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>161844</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>146124</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>307967</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>157368</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>143308</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>302734</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>164480</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>147140</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>310850</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>903</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>670086</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>610580</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1280666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>662166</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>605009</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1271217</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>676812</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>614005</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1288279</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>